--- a/AAII_Financials/Quarterly/PFG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PFG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>PFG</t>
   </si>
@@ -656,316 +656,322 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3905800</v>
+      </c>
+      <c r="E8" s="3">
         <v>3529100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4576700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3681600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3671300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3695900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4752000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3011600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4310800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4053300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2690800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4598700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3557300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2819000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3803000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3387600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3597200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3095500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4091100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3423700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3539400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3208500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3765100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3310700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3114600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4551300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4055500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4469500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3989900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3750700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3777200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4351700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3243900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2893500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3259900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4644400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3192500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3078200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3542800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2829300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2023400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1627000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2557800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2055000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1858500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2241300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2284500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1915500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2546600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2097300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2487100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1689300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1857900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1791500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1882400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1902100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2018900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1626600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1812800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1454600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2467500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1096100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1764200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1956000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>203700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2909400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1699400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1027500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,8 +1514,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1513,8 +1532,8 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
@@ -1531,85 +1550,88 @@
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>8300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>11100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>17300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>6600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>3600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>9900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>22200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>16600</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>14200</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>28800</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>29000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E15" s="3">
         <v>39600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>128400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>41000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>41200</v>
+      </c>
+      <c r="I15" s="3">
         <v>41700</v>
       </c>
-      <c r="H15" s="3">
-        <v>41700</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>115500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>46900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>48700</v>
-      </c>
-      <c r="L15" s="3">
-        <v>68200</v>
       </c>
       <c r="M15" s="3">
         <v>68200</v>
       </c>
       <c r="N15" s="3">
-        <v>74000</v>
+        <v>68200</v>
       </c>
       <c r="O15" s="3">
         <v>74000</v>
@@ -1618,7 +1640,7 @@
         <v>74000</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>74000</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1635,8 +1657,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>5</v>
@@ -1653,20 +1675,20 @@
       <c r="AB15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC15" s="3">
-        <v>3800</v>
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD15" s="3">
         <v>3800</v>
       </c>
       <c r="AE15" s="3">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="AF15" s="3">
         <v>3500</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>5</v>
+      <c r="AG15" s="3">
+        <v>3500</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>5</v>
@@ -1677,8 +1699,8 @@
       <c r="AJ15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK15" s="3">
-        <v>0</v>
+      <c r="AK15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL15" s="3">
         <v>0</v>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3424000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3006800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3931000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3429200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3153900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3632300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3648400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3251400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3867300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3440700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3777500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2975400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3110600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3034400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3156700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2969300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2589600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2708200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3482100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2995600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3106800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2594600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3173500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3035600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2616000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4223100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3684000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4123500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3539400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3224400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3534300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3782600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2728500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2436500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2945100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3486600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2826900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2664200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3161500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2458600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>481800</v>
+      </c>
+      <c r="E18" s="3">
         <v>522300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>645700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>252400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>517400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>63600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1103600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-239800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>443500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>612600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1086700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1623300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>446700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-215400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>646300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>418300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1007600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>387300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>609000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>428100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>432600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>613900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>591600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>275100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>498600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>328200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>371500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>346000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>450500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>526300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>242900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>569100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>515400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>457000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>314800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1157800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>365600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>414000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>381300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>370700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,65 +2056,66 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E20" s="3">
         <v>40500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>34700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>54000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-14500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>20500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>18400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-648700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1222100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2963000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8900</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -2146,53 +2179,56 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>537500</v>
+      </c>
+      <c r="E21" s="3">
         <v>521400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>764000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>289400</v>
       </c>
-      <c r="G21" s="3">
-        <v>544800</v>
-      </c>
       <c r="H21" s="3">
+        <v>544300</v>
+      </c>
+      <c r="I21" s="3">
         <v>70600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1227900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-246900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>492600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>695300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1039000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1678900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>527600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-138500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2226,50 +2262,53 @@
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>496100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>574200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>586000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>636200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>413300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>641900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>631000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>580600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>426500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1274000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>467600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>514400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>449400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>509500</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2330,8 +2369,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>5</v>
@@ -2348,21 +2387,21 @@
       <c r="AB22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>300</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH22" s="3" t="s">
         <v>5</v>
       </c>
@@ -2372,8 +2411,8 @@
       <c r="AJ22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
+      <c r="AK22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>496300</v>
+      </c>
+      <c r="E23" s="3">
         <v>481800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>635600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>248400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>503100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>28900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1112400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-293800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>443900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>627100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1107200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1604900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>453600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-212500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1640400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3970600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>378400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>609000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>428100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>432600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>613900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>591600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>275100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>498600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>328200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>371300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>345700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>450300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>526000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>242900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>569100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>515400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>457000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>314800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1157800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>365600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>414000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>381300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>370700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E24" s="3">
         <v>68900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>110400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>69600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-34000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>209900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>87100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>95100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-268000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>354800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>59900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>328800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>836700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>35200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>103800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>63800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>61000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>97600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>39200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>82500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>43200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>56000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>61100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>58200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>73900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>11200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>109100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>55900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>54500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>68600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>344600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>50800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>60400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>43100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>43300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>430300</v>
+      </c>
+      <c r="E26" s="3">
         <v>412900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>525200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>233900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>433500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>62900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>902500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-193400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>356800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>532000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-839200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1250100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>393700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-134500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1311600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3133900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>343200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>505200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>364300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>371600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>516300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>491500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>235900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>416100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>285000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>315300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>284600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>392100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>452100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>231700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>460000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>459500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>402500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>246200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>813200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>314800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>353600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>338200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>327400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>403400</v>
+      </c>
+      <c r="E27" s="3">
         <v>424600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>517000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>213800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>406200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>48100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>905400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-220000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>353100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>532500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-871700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1246200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>388800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-140100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1315700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3118700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>338700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>471800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>359900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>361800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>517100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>472600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>236000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>398300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>288900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>300900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>277100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>386300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>429900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>236500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>456300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>456600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>397100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>245100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>810200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>309500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>348900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>318000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>308200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>596700</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,65 +3554,68 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-40500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-34700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-54000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>14500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-20500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-18400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>648700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1222100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2963000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8900</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -3610,130 +3679,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>403400</v>
+      </c>
+      <c r="E33" s="3">
         <v>424600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>517000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>213800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>406200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>48100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>905400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-220000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>353100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>532500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-871700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1246200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>388800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-140100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1315700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3118700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>338700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>471800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>359900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>361800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>517100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>472600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>236000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>398300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>288900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>300900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>277100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>386300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>429900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>236500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>456300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>456600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>397100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>841800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>810200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>309500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>348900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>318000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>308200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>403400</v>
+      </c>
+      <c r="E35" s="3">
         <v>424600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>517000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>213800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>406200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>48100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>905400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-220000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>353100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>532500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-871700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1246200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>388800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-140100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1315700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3118700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>338700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>471800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>359900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>361800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>517100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>472600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>236000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>398300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>288900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>300900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>277100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>386300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>429900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>236500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>456300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>456600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>397100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>841800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>810200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>309500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>348900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>318000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>308200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5259500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4054000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4431000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5137100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3659000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3875700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4211900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6174500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4816600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4168400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4707700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4564300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4073900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4640900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4848000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4239600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3173100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2741200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2332000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3145400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2417400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2003500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2849800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3556700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3150400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3482700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2515900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3198000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3315900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2259700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2977500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2926700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2342000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2335700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2470800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2795000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2006400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1534700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2719600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2218200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1108200</v>
+      </c>
+      <c r="E42" s="3">
         <v>1285000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1260700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1379600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1260900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1338300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1058700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>914500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>834900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>936700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>915500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>789700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>792800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>887500</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,130 +4524,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1281800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1103300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1344600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1182300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1204800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1144800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1126400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4350100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4583900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4486700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1361500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4529900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4566600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4554700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3933300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4336600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4683900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2374400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1842400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1713200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1675700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1708300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1723800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1530200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1760000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1691000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1740300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1635700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1549200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1641100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1413100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1514400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1455600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1638400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1469800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1516600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1381400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1447000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1361900</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1382800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24298900</v>
+      </c>
+      <c r="E45" s="3">
         <v>23971400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24196100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24298200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>24105600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24025600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>24136600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21360100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20928900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21196800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24909300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21249800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21351000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21966300</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31948400</v>
+      </c>
+      <c r="E46" s="3">
         <v>30413700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>31232400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31997200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>30230300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>30384400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>30533600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>32799200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>31164300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30788600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>31894000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31133700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>30784300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32049400</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,374 +5024,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>85199600</v>
+      </c>
+      <c r="E47" s="3">
         <v>83389100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>82225400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>80737300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>79525600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>79175500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>76054600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>77375000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>73852300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>73672800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>72047100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>68999400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>71447000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>72447900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>93004900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>91706600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>95768100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>101043300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>106830500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>104928800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>104033300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>102928500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>104509600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>101252000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>98858900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>94157700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>96056700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>94038200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>90903700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>88324000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>84766600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>84007200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>82404800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>81952800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>82102700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>81203400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>79050500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>77812000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>75835500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>77758500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>778700</v>
+      </c>
+      <c r="E48" s="3">
         <v>714900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>701400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>716200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>724700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>742700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>769400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>798200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>805900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>913500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>938400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>958100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>957700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>986200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3235800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3142900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3066900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3159800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3113400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3031000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2972400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2877100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2816300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2780600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2692800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>973800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>967700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>961700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>959500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>933200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>767300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>770600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>762900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>775200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>759500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>754600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>750300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>718800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>699000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>674500</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6960600</v>
+      </c>
+      <c r="E49" s="3">
         <v>6950500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6939100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6903400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6914100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6892000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6946500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7013700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6961700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6970100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7028800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7022400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7106600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7119900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3131500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3072900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3134500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3262300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3228200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3277800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3377100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3399300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3434000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3358800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3340200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3333000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3480500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3492400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2412200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2420900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2415100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2482600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2458600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2489100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2383500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2369900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2344600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2355500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2346100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2381100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,53 +5649,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>205707000</v>
+      </c>
+      <c r="E52" s="3">
         <v>189051100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>198219900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>192410800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>184001900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>174513700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>177808900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>183818400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>174715100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>175005600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>171967100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>158589000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>167453400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>165197700</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>352752300</v>
+      </c>
+      <c r="E54" s="3">
         <v>332704500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>341376500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>334491800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>323103800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>313003300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>313663600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>322857700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>308777300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>308683500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>305046700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>287948000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>299186900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>299408200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>290867000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>282580600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>293220200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>291538500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>304657200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>298908400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>302165500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>295634600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>296627700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>278484800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>271309400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>246903900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>276087800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>270238400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>267918000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>259419900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>243036100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>258758300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>252104000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>253636500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>253941200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>247933600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>240153900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>235496000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>228014300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>230367600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1323700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1334800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1342400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1344400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1363800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1378700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1379900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1315400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1295000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1405900</v>
       </c>
       <c r="M57" s="3">
         <v>1405900</v>
       </c>
       <c r="N57" s="3">
+        <v>1405900</v>
+      </c>
+      <c r="O57" s="3">
         <v>1381900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1401400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1396200</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,297 +6239,306 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>576400</v>
+      </c>
+      <c r="E58" s="3">
         <v>239200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>648600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>215500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>247000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>669100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>882400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>270600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>384800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>419100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>418000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>599200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>454100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>438100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>80700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>66500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>66900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>279400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>79800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>74300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>82700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>84000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>84700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>76600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>76300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>105600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>93400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>96100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>76800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>43900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>42900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>36100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>64500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>78100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>39500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>58800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>42000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>59500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>51400</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18247600</v>
+      </c>
+      <c r="E59" s="3">
         <v>18352300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18692000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18987800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18913000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18939500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18804000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19268300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18710700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19230500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20271200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18667400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20031100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20643400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>219567200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>211885500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>221191300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>218522100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>227029900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>222751400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>226757000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>221945000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>220270800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>204706300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>199248400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>179838200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>208008600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>202512800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>203727800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>198723000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>185601300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>201994800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>196987200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>198011900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>198294200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>193274400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>188508900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>185386500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>178689500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>179763600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20147700</v>
+      </c>
+      <c r="E60" s="3">
         <v>19926300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20683000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20547700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20523800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20987300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21066300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20854300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20390500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21055500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22095100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20648500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21886600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22477700</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3974500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3927700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3677800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3924600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3923000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3921300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3775100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3932900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3932200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3931500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4181300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3930200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3992900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4688600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3997000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3981000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4280700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4280400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4280200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4279700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4279500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4279400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4279200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4279000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4163400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3670100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3765900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3797400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3795400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3302000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3259600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3245500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3219900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3196600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3178400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3175400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3126800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3126200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3125700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3278200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>313808500</v>
+      </c>
+      <c r="E62" s="3">
         <v>294593600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>302367300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>296097500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>285029600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>274713100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>275215000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>284707000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>271378500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>270366600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>265465100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>250905500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>261245200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>260291300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1324200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1079300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1421800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1373900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2320200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2345600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2324600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2065900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2330800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2106900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2061500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1450300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1796600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1928100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1687500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1318700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>958400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>911400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>887900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>909000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1092500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1515200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1281800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1048100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>972400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1229900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>339862800</v>
+      </c>
+      <c r="E66" s="3">
         <v>320311700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>328985200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>322363800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>311245300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>301408300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>302194600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>311264500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>297440900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>297082300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>293836100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>276965600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>288530700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>288874700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>280890300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>273134400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>282183400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>279640900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>288587800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>282837700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>285932400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>280229100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>280068800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>262833900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>256066300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>233996400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>261469800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>255434200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>253883300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>246725500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>231646100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>247057500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>240464700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>241449600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>241091900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>235937200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>228985800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>224879900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>217787000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>219573000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18542200</v>
+      </c>
+      <c r="E72" s="3">
         <v>18318900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18071300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17730000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17692600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17459300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17583500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16847000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17235300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17050600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16683500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17717000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16629900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16398800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16697300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17210900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15985600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13090800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12884500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12583900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12395000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12199200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11838000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>11521400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11441400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11198800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11074300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10927800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10805800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10571900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10290200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10207900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9904300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9598300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9482900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>8784600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8112200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>7937400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>7720400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>7528100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12142800</v>
+      </c>
+      <c r="E76" s="3">
         <v>11815300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11883900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11665500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11415300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11216800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11086400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11237400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11013400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11185500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10916000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10671600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10344500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10217900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9976700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9446200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11036800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11897600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16069400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16070700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16233100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15405500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16558900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15650900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15243100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12907500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14618000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14804200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14034700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12694400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11390000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11700800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11639300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12186900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12849300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>11996400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>11168100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>10616100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>10227300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>10794600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>403400</v>
+      </c>
+      <c r="E81" s="3">
         <v>424600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>517000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>213800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>406200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>48100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>905400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-220000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>353100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>532500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-871700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1246200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>388800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-140100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1315700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3118700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>338700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>471800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>359900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>361800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>517100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>472600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>236000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>398300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>288900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>300900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>277100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>386300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>429900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>236500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>456300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>456600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>397100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>841800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>810200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>309500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>348900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>318000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>308200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,52 +8961,53 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E83" s="3">
         <v>41700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>49400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>140700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-48700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>48700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>204100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>225200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8841,53 +9039,56 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>124600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>228200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>135500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>109900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>170400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>72800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>115600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>123600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>111700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>116200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>102000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>100400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>68100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>138800</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2077400</v>
+      </c>
+      <c r="E89" s="3">
         <v>187100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1743700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1003800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>811900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>977300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1459000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1128000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1431700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>584200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>944000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1050600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1102500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>695300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1163200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1171000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>807200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>31500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1111800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>973400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>992800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>140800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>628200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1064300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>457000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1589100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1028400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1786400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1502000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1176400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1442600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2075700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>891700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>746500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>559300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1799600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1306200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>522900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>930500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>801700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-67600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-34400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-30000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-34600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-25400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-21000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-22900</v>
       </c>
       <c r="X91" s="3">
         <v>-22900</v>
       </c>
       <c r="Y91" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-36500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-34300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-32700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-29800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-17600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-31500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-60300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-43800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-45800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-34400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1421200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-959800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3101200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>167800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-249700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-952700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3770400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-287800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1343200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-215000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-49500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>21700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1104100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>568500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>587900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-224700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>126800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2790800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1924500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>76400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1019200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1385900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1418800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1308400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-912700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2762300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2582200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-852900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1491100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1293800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2067200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1361600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-979900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-735100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-813400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-673300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1831000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-656300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-823600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>176500</v>
+      </c>
+      <c r="E96" s="3">
         <v>173500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>172400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>172900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>169700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>169000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>165700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>165100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>165200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>162400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>159000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>156100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>154900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>155500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-156200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-157400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-161700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-167000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-168500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-168200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-165200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-152200</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-153700</v>
       </c>
       <c r="Z96" s="3">
         <v>-153700</v>
       </c>
       <c r="AA96" s="3">
+        <v>-153700</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-153500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-153600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-152400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-153000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-150400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-150200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-152100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-150700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-148500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-147300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-141500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-135800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-132700</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-130000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-123800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-117900</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>549300</v>
+      </c>
+      <c r="E100" s="3">
         <v>395700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>651400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>306500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-778900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-360800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>348800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>227500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-495700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>219700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-585600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-510700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1691200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>201700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1123300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-692400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-150600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>250900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>865600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1679100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-655300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>32100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>50800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>760800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>519100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>290400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1051800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>677900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>407100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-403100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-98000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>576200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>476200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>98300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-148400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-197600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-161200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>123200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>227200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-15300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1205500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-377000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-706100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1478100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-216700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-336200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1962600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1357900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>648200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-539300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>143400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>490400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-567000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-207100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>608400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1066500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>431900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>409200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-813400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>728000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>413900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-846300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-706900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>406300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-332300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>966800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-682100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-117900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1056200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-717800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>50800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>584700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-135100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-324200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>788600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>471700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1184900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>501400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-37200</v>
       </c>
     </row>
